--- a/ba/Diary.xlsx
+++ b/ba/Diary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\Documents\BA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\vim_files\ba\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBAEA0C0-6181-447A-88E2-357D7DE8DCB4}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B6E1BC-9EDC-4F09-988F-CED5A68A30FB}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DE023FCE-4914-492D-AF3C-3FBC726999DB}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Yolo-Model von Jonas Hendl von Festplatte auf PC übertragen, readme gelesen und Ordnerstruktur angesehen</t>
   </si>
@@ -47,13 +47,16 @@
   <si>
     <t>Lesen von Tutorial (https://www.pyimagesearch.com/2018/07/23/simple-object-tracking-with-opencv/) und Papers (https://arxiv.org/pdf/1902.00615.pdf, https://www.vision.ee.ethz.ch/en/publications/papers/proceedings/eth_biwi_00753.pdf)</t>
   </si>
+  <si>
+    <t>Programmieren von Standard opencv Trackern und code um Videos Frame by Frame anzusehen</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -86,7 +89,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -456,6 +459,9 @@
         <f t="shared" si="0"/>
         <v>43851</v>
       </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">

--- a/ba/Diary.xlsx
+++ b/ba/Diary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\vim_files\ba\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B6E1BC-9EDC-4F09-988F-CED5A68A30FB}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC676F27-ED51-48E8-9687-D2AB48C321F5}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DE023FCE-4914-492D-AF3C-3FBC726999DB}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Yolo-Model von Jonas Hendl von Festplatte auf PC übertragen, readme gelesen und Ordnerstruktur angesehen</t>
   </si>
@@ -49,6 +49,15 @@
   </si>
   <si>
     <t>Programmieren von Standard opencv Trackern und code um Videos Frame by Frame anzusehen</t>
+  </si>
+  <si>
+    <t>Anwendung der Tensorflow-Models auf Bahn-Videos/Vergleich verschieder Models und Videoabschnitten, Optical Flow Tutorial clonen und testen, https://docs.opencv.org/3.4/d4/dee/tutorial_optical_flow.html</t>
+  </si>
+  <si>
+    <t>Lesen, https://www.learnopencv.com/object-tracking-using-opencv-cpp-python/</t>
+  </si>
+  <si>
+    <t>Klassendefinitionen der Yolo Implementierung untersuchen und passende Models finden (kein Model gefunden welches auf 52(53) Klassen passt, 52 sind in Klassendefinition.names definiert)</t>
   </si>
 </sst>
 </file>
@@ -58,10 +67,24 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -84,14 +107,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -486,17 +512,26 @@
         <f t="shared" si="0"/>
         <v>43855</v>
       </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>43856</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>43857</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
